--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4cn.xlsx
@@ -453,7 +453,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -639,6 +639,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -648,7 +651,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -833,6 +836,9 @@
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>9376392.18772012</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
               </c:numCache>
@@ -876,7 +882,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1062,6 +1068,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1071,7 +1080,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1257,6 +1266,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>16585564.304557247</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>17355066.429656375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1299,7 +1311,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1485,6 +1497,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1494,7 +1509,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1680,6 +1695,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>7209172.1168371271</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>7978674.2419362552</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1701,11 +1719,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="445511168"/>
-        <c:axId val="445513088"/>
+        <c:axId val="460842496"/>
+        <c:axId val="466223872"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="445511168"/>
+        <c:axId val="460842496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1748,14 +1766,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="445513088"/>
+        <c:crossAx val="466223872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="445513088"/>
+        <c:axId val="466223872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1806,7 +1824,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="445511168"/>
+        <c:crossAx val="460842496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1997,7 +2015,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2183,6 +2201,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-329147.77001413936</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-915628.10722505616</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2197,8 +2218,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="576494208"/>
-        <c:axId val="576285696"/>
+        <c:axId val="466249984"/>
+        <c:axId val="466248448"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2223,7 +2244,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2409,6 +2430,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2418,7 +2442,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2604,6 +2628,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>5.970703125</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6.2764160156250002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2620,11 +2647,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="498730880"/>
-        <c:axId val="498759552"/>
+        <c:axId val="466245120"/>
+        <c:axId val="466246656"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="498730880"/>
+        <c:axId val="466245120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2667,14 +2694,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="498759552"/>
+        <c:crossAx val="466246656"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="498759552"/>
+        <c:axId val="466246656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2725,12 +2752,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="498730880"/>
+        <c:crossAx val="466245120"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="576285696"/>
+        <c:axId val="466248448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2767,12 +2794,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="576494208"/>
+        <c:crossAx val="466249984"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="576494208"/>
+        <c:axId val="466249984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2781,7 +2808,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="576285696"/>
+        <c:crossAx val="466248448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3190,7 +3217,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -5894,6 +5921,44 @@
         <v>1556859.6476140034</v>
       </c>
     </row>
+    <row r="65" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="14">
+        <v>46203</v>
+      </c>
+      <c r="B65" s="15">
+        <v>6.2764160156250002</v>
+      </c>
+      <c r="C65" s="15">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D65" s="16">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E65" s="16">
+        <v>-915628.10722505616</v>
+      </c>
+      <c r="F65" s="17">
+        <v>-145883.90969394316</v>
+      </c>
+      <c r="G65" s="17">
+        <v>2371190.6026890925</v>
+      </c>
+      <c r="H65" s="17">
+        <v>14882578.674817316</v>
+      </c>
+      <c r="I65" s="17">
+        <v>9376392.18772012</v>
+      </c>
+      <c r="J65" s="17">
+        <v>17355066.429656375</v>
+      </c>
+      <c r="K65" s="17">
+        <v>7978674.2419362552</v>
+      </c>
+      <c r="L65" s="16">
+        <v>2472487.7548390594</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4cn.xlsx
@@ -453,7 +453,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -642,6 +642,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -651,7 +654,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -839,6 +842,9 @@
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
                 <c:pt idx="62">
+                  <c:v>9376392.18772012</c:v>
+                </c:pt>
+                <c:pt idx="63">
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
               </c:numCache>
@@ -882,7 +888,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1071,6 +1077,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1080,7 +1089,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1269,6 +1278,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>17355066.429656375</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>14891650.637779195</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1311,7 +1323,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1500,6 +1512,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1509,7 +1524,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1698,6 +1713,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>7978674.2419362552</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5515258.4500590749</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1719,11 +1737,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="460842496"/>
-        <c:axId val="466223872"/>
+        <c:axId val="514734720"/>
+        <c:axId val="527824768"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="460842496"/>
+        <c:axId val="514734720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1766,14 +1784,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="466223872"/>
+        <c:crossAx val="527824768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="466223872"/>
+        <c:axId val="527824768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1824,7 +1842,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="460842496"/>
+        <c:crossAx val="514734720"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2015,7 +2033,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2204,6 +2222,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>-915628.10722505616</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-314574.39222416701</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2218,8 +2239,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="466249984"/>
-        <c:axId val="466248448"/>
+        <c:axId val="704142336"/>
+        <c:axId val="703807872"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2244,7 +2265,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2433,6 +2454,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2442,7 +2466,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2631,6 +2655,9 @@
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>6.2764160156250002</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5.2375219726562499</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2647,11 +2674,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="466245120"/>
-        <c:axId val="466246656"/>
+        <c:axId val="698675968"/>
+        <c:axId val="698677888"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="466245120"/>
+        <c:axId val="698675968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2694,14 +2721,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="466246656"/>
+        <c:crossAx val="698677888"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="466246656"/>
+        <c:axId val="698677888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2752,12 +2779,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="466245120"/>
+        <c:crossAx val="698675968"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="466248448"/>
+        <c:axId val="703807872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2794,12 +2821,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="466249984"/>
+        <c:crossAx val="704142336"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="466249984"/>
+        <c:axId val="704142336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2808,7 +2835,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="466248448"/>
+        <c:crossAx val="703807872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3217,7 +3244,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG65"/>
+  <dimension ref="A1:AG66"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -5959,6 +5986,44 @@
         <v>2472487.7548390594</v>
       </c>
     </row>
+    <row r="66" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A66" s="14">
+        <v>46234</v>
+      </c>
+      <c r="B66" s="15">
+        <v>5.2375219726562499</v>
+      </c>
+      <c r="C66" s="15">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D66" s="16">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E66" s="16">
+        <v>-314574.39222416701</v>
+      </c>
+      <c r="F66" s="17">
+        <v>-60061.684488672065</v>
+      </c>
+      <c r="G66" s="17">
+        <v>2311128.9182004202</v>
+      </c>
+      <c r="H66" s="17">
+        <v>12104588.490715969</v>
+      </c>
+      <c r="I66" s="17">
+        <v>9376392.18772012</v>
+      </c>
+      <c r="J66" s="17">
+        <v>14891650.637779195</v>
+      </c>
+      <c r="K66" s="17">
+        <v>5515258.4500590749</v>
+      </c>
+      <c r="L66" s="16">
+        <v>2787062.1470632264</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4cn.xlsx
@@ -453,7 +453,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -645,6 +645,9 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -654,7 +657,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -845,6 +848,9 @@
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
                 <c:pt idx="63">
+                  <c:v>9376392.18772012</c:v>
+                </c:pt>
+                <c:pt idx="64">
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
               </c:numCache>
@@ -888,7 +894,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1080,6 +1086,9 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1089,7 +1098,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1281,6 +1290,9 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>14891650.637779195</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>14989831.863008782</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1323,7 +1335,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1515,6 +1527,9 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1524,7 +1539,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1716,6 +1731,9 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>5515258.4500590749</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5613439.6752886623</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1737,11 +1755,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="514734720"/>
-        <c:axId val="527824768"/>
+        <c:axId val="374257536"/>
+        <c:axId val="374272000"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="514734720"/>
+        <c:axId val="374257536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1784,14 +1802,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527824768"/>
+        <c:crossAx val="374272000"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="527824768"/>
+        <c:axId val="374272000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1842,7 +1860,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="514734720"/>
+        <c:crossAx val="374257536"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2033,7 +2051,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2225,6 +2243,9 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>-314574.39222416701</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-309173.41467680095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2239,8 +2260,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="704142336"/>
-        <c:axId val="703807872"/>
+        <c:axId val="495988096"/>
+        <c:axId val="495986176"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2265,7 +2286,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2457,6 +2478,9 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2466,7 +2490,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="64"/>
+                <c:ptCount val="65"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2658,6 +2682,9 @@
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>5.2375219726562499</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5.2800039062500002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2674,11 +2701,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="698675968"/>
-        <c:axId val="698677888"/>
+        <c:axId val="495127552"/>
+        <c:axId val="495984640"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="698675968"/>
+        <c:axId val="495127552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2721,14 +2748,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="698677888"/>
+        <c:crossAx val="495984640"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="698677888"/>
+        <c:axId val="495984640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2779,12 +2806,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="698675968"/>
+        <c:crossAx val="495127552"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="703807872"/>
+        <c:axId val="495986176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2821,12 +2848,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="704142336"/>
+        <c:crossAx val="495988096"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="704142336"/>
+        <c:axId val="495988096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2835,7 +2862,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="703807872"/>
+        <c:crossAx val="495986176"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3244,7 +3271,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG66"/>
+  <dimension ref="A1:AG67"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -6024,6 +6051,44 @@
         <v>2787062.1470632264</v>
       </c>
     </row>
+    <row r="67" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A67" s="14">
+        <v>46265</v>
+      </c>
+      <c r="B67" s="15">
+        <v>5.2800039062500002</v>
+      </c>
+      <c r="C67" s="15">
+        <v>35.77999878</v>
+      </c>
+      <c r="D67" s="16">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E67" s="16">
+        <v>-309173.41467680095</v>
+      </c>
+      <c r="F67" s="17">
+        <v>-58555.527640960434</v>
+      </c>
+      <c r="G67" s="17">
+        <v>2252573.3905594596</v>
+      </c>
+      <c r="H67" s="17">
+        <v>11893596.301268755</v>
+      </c>
+      <c r="I67" s="17">
+        <v>9376392.18772012</v>
+      </c>
+      <c r="J67" s="17">
+        <v>14989831.863008782</v>
+      </c>
+      <c r="K67" s="17">
+        <v>5613439.6752886623</v>
+      </c>
+      <c r="L67" s="16">
+        <v>3096235.5617400273</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
